--- a/distinta_vuota.xlsx
+++ b/distinta_vuota.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Server\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CF3A49-737B-4A54-9476-6BFBECA22180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F55599E-D028-41C5-9A2E-06F1F2BD27A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BF18F4E-3627-49D6-B6A0-5A92BEB215F1}"/>
+    <workbookView xWindow="1950" yWindow="1635" windowWidth="11820" windowHeight="14565" xr2:uid="{7BF18F4E-3627-49D6-B6A0-5A92BEB215F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Convocati" sheetId="2" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>Sede: Via del Purgatorio 81/a - 0574633593</t>
   </si>
   <si>
-    <t>Stagione sportiva 2025/2026</t>
-  </si>
-  <si>
     <t>Distinta dei giocatori partecipanti alla gara:</t>
   </si>
   <si>
@@ -107,6 +104,9 @@
   </si>
   <si>
     <t>Campionato</t>
+  </si>
+  <si>
+    <t>Stagione sportiva 2026/2027</t>
   </si>
 </sst>
 </file>
@@ -356,41 +356,41 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,44 +719,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="35" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="22"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="34"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="23"/>
@@ -771,14 +771,14 @@
       <c r="K4" s="25"/>
     </row>
     <row r="5" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="27" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="28" t="s">
         <v>3</v>
       </c>
       <c r="H5" s="15"/>
@@ -787,15 +787,15 @@
       <c r="K5" s="16"/>
     </row>
     <row r="6" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>4</v>
+      <c r="B6" s="29" t="s">
+        <v>26</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
-      <c r="G6" s="19" t="s">
-        <v>5</v>
+      <c r="G6" s="28" t="s">
+        <v>4</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -804,14 +804,14 @@
     </row>
     <row r="7" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="29" t="s">
-        <v>24</v>
+      <c r="G7" s="27" t="s">
+        <v>23</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15"/>
@@ -819,13 +819,13 @@
       <c r="K7" s="16"/>
     </row>
     <row r="8" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="30"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="16"/>
-      <c r="G8" s="19" t="s">
-        <v>25</v>
+      <c r="G8" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
@@ -833,13 +833,13 @@
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="19"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="16"/>
-      <c r="G9" s="19" t="s">
-        <v>6</v>
+      <c r="G9" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="H9" s="15"/>
       <c r="I9" s="15"/>
@@ -847,7 +847,7 @@
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="2:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -860,34 +860,34 @@
     </row>
     <row r="11" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="I11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
@@ -1191,7 +1191,7 @@
       <c r="K36" s="10"/>
     </row>
     <row r="37" spans="2:11" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="17"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="15"/>
       <c r="D37" s="15"/>
       <c r="E37" s="15"/>
@@ -1203,103 +1203,103 @@
       <c r="K37" s="16"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="31"/>
+      <c r="D38" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="26" t="s">
+      <c r="E38" s="32"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="13" t="s">
+      <c r="H38" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="H38" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="27"/>
+      <c r="I38" s="31"/>
       <c r="J38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K38" s="13" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="18"/>
+      <c r="B39" s="33"/>
       <c r="C39" s="16"/>
-      <c r="D39" s="19"/>
+      <c r="D39" s="28"/>
       <c r="E39" s="15"/>
       <c r="F39" s="16"/>
       <c r="G39" s="12"/>
-      <c r="H39" s="19"/>
+      <c r="H39" s="28"/>
       <c r="I39" s="16"/>
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="18"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="16"/>
-      <c r="D40" s="19"/>
+      <c r="D40" s="28"/>
       <c r="E40" s="15"/>
       <c r="F40" s="16"/>
       <c r="G40" s="12"/>
-      <c r="H40" s="19"/>
+      <c r="H40" s="28"/>
       <c r="I40" s="16"/>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="18"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="16"/>
-      <c r="D41" s="19"/>
+      <c r="D41" s="28"/>
       <c r="E41" s="15"/>
       <c r="F41" s="16"/>
       <c r="G41" s="12"/>
-      <c r="H41" s="19"/>
+      <c r="H41" s="28"/>
       <c r="I41" s="16"/>
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="18"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="16"/>
-      <c r="D42" s="19"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="15"/>
       <c r="F42" s="16"/>
       <c r="G42" s="12"/>
-      <c r="H42" s="19"/>
+      <c r="H42" s="28"/>
       <c r="I42" s="16"/>
       <c r="J42" s="12"/>
       <c r="K42" s="12"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="18"/>
+      <c r="B43" s="33"/>
       <c r="C43" s="16"/>
-      <c r="D43" s="19"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="15"/>
       <c r="F43" s="16"/>
       <c r="G43" s="12"/>
-      <c r="H43" s="19"/>
+      <c r="H43" s="28"/>
       <c r="I43" s="16"/>
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="18"/>
+      <c r="B44" s="33"/>
       <c r="C44" s="16"/>
-      <c r="D44" s="19"/>
+      <c r="D44" s="28"/>
       <c r="E44" s="15"/>
       <c r="F44" s="16"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="19"/>
+      <c r="H44" s="28"/>
       <c r="I44" s="16"/>
       <c r="J44" s="12"/>
       <c r="K44" s="12"/>
     </row>
     <row r="45" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="17"/>
+      <c r="B45" s="14"/>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
       <c r="E45" s="15"/>
@@ -1311,18 +1311,18 @@
       <c r="K45" s="16"/>
     </row>
     <row r="46" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="22"/>
+      <c r="B46" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="19"/>
     </row>
     <row r="47" spans="2:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="23"/>
@@ -1337,7 +1337,7 @@
       <c r="K47" s="25"/>
     </row>
     <row r="48" spans="2:11" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="17"/>
+      <c r="B48" s="14"/>
       <c r="C48" s="15"/>
       <c r="D48" s="15"/>
       <c r="E48" s="15"/>
@@ -1349,15 +1349,15 @@
       <c r="K48" s="16"/>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" s="14" t="s">
-        <v>22</v>
+      <c r="B49" s="34" t="s">
+        <v>21</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
       <c r="E49" s="15"/>
       <c r="F49" s="16"/>
-      <c r="G49" s="14" t="s">
-        <v>23</v>
+      <c r="G49" s="34" t="s">
+        <v>22</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
@@ -1365,12 +1365,12 @@
       <c r="K49" s="16"/>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B50" s="17"/>
+      <c r="B50" s="14"/>
       <c r="C50" s="15"/>
       <c r="D50" s="15"/>
       <c r="E50" s="15"/>
       <c r="F50" s="16"/>
-      <c r="G50" s="17"/>
+      <c r="G50" s="14"/>
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
       <c r="J50" s="15"/>
@@ -1378,6 +1378,35 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="B45:K45"/>
+    <mergeCell ref="B46:K47"/>
+    <mergeCell ref="B48:K48"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="H39:I39"/>
     <mergeCell ref="B10:K10"/>
     <mergeCell ref="B1:F4"/>
     <mergeCell ref="G1:K4"/>
@@ -1390,35 +1419,6 @@
     <mergeCell ref="G8:K8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="G9:K9"/>
-    <mergeCell ref="B37:K37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="G49:K49"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="G50:K50"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="B45:K45"/>
-    <mergeCell ref="B46:K47"/>
-    <mergeCell ref="B48:K48"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
